--- a/VerveStacks_THA_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_THA_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_THA_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{567E497D-D75F-4A3C-976C-3CDA82A13C04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{66706F00-458F-4FFD-80AB-13004BC15F5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -934,18 +934,108 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_THA_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_THA_029</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_THA_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_THA_025</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_THA_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_THA_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_THA_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_THA_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_THA_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_THA_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_THA_028</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_THA_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_THA_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_THA_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_THA_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_THA_027</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 27</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_THA_020</t>
   </si>
   <si>
@@ -958,34 +1048,46 @@
     <t>connecting solar to buses in cluster 3</t>
   </si>
   <si>
-    <t>distr_solelc_spv_THA_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_THA_029</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_THA_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_THA_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_THA_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
+    <t>distr_solelc_spv_THA_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_THA_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_THA_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_THA_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_THA_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_THA_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_THA_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
   </si>
   <si>
     <t>distr_solelc_spv_THA_018</t>
@@ -1006,120 +1108,63 @@
     <t>connecting solar to buses in cluster 26</t>
   </si>
   <si>
-    <t>distr_solelc_spv_THA_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_THA_025</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 25</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_THA_005</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 5</t>
   </si>
   <si>
-    <t>distr_solelc_spv_THA_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_THA_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_THA_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_THA_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_THA_028</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_THA_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_THA_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_THA_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_THA_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_THA_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_THA_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_THA_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_THA_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_THA_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_THA_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_TH82-500_THA,e_w876135539-500_THA,e_TH81-230_THA</t>
+  </si>
+  <si>
+    <t>e_w334185872-230_THA,e_w262815047-230_THA,e_w254460966-230_THA,e_w631215304-230_THA,e_TH28-500_THA,e_w401936547-500_THA,e_w401936547-230_THA,e_w1192398379-230_THA,e_TH22-230_THA</t>
+  </si>
+  <si>
+    <t>e_w813762139-230_THA,e_w384684882-230_THA,e_w196803560-230_THA,e_TH16-230_THA,e_TH8-500_THA,e_TH7-500_THA,e_w551229222-230_THA,e_w259533943-500_THA,e_TH1-500_THA</t>
+  </si>
+  <si>
+    <t>e_TH31-230_THA,e_w1357836334-230_THA,e_w377077088-230_THA</t>
+  </si>
+  <si>
+    <t>e_w550957004-230_THA,e_w1415498617-500_THA,e_TH86-230_THA,e_w550922890-230_THA,e_w244062167-230_THA,e_TH85-230_THA,e_w295988731-230_THA</t>
+  </si>
+  <si>
+    <t>e_TH47-230_THA,e_w404563246-230_THA,e_TH30-230_THA,e_w904473776-230_THA,e_w1364467990-230_THA,e_w550636268-230_THA,e_TH44-230_THA,e_w550657165-230_THA</t>
+  </si>
+  <si>
+    <t>e_w650122709-230_THA,e_TH71-500_THA,e_TH49-500_THA,e_TH74-230_THA,e_w404291513-230_THA,e_TH78-230_THA,e_w551510148-230_THA</t>
+  </si>
+  <si>
+    <t>e_w551510148-230_THA,e_TH44-230_THA,e_TH78-230_THA,e_w550657165-230_THA,e_w1387094571-230_THA</t>
+  </si>
+  <si>
+    <t>e_TH17-230_THA,e_w1281883109-230_THA,e_TH31-230_THA,e_w377077088-230_THA</t>
+  </si>
+  <si>
+    <t>e_TH31-230_THA</t>
+  </si>
+  <si>
+    <t>e_w550152207-230_THA,e_w199773777-500_THA,e_w772281525-230_THA,e_TH75-230_THA,e_TH69-230_THA,e_w404006545-230_THA,e_w659641345-230_THA,e_w658704544-500_THA</t>
+  </si>
+  <si>
+    <t>e_w1281883109-230_THA</t>
+  </si>
+  <si>
+    <t>e_w324258748-230_THA,e_w238578822-230_THA,e_TH89-230_THA</t>
+  </si>
+  <si>
+    <t>e_TH22-230_THA,e_w659646706-230_THA,e_w550224444-230_THA,e_w550296523-230_THA,e_w659647773-230_THA,e_TH20-230_THA,e_w550257735-230_THA,e_TH13-500_THA,e_w382334126-230_THA,e_w343034987-500_THA,e_w382334127-230_THA,e_w247878196-230_THA,e_w245311456-230_THA</t>
+  </si>
+  <si>
+    <t>e_TH9-500_THA,e_w658429244-230_THA,e_w247704837-230_THA</t>
+  </si>
+  <si>
     <t>e_w261489769-500_THA,e_w262815047-230_THA,e_w334185872-230_THA,e_TH51-500_THA,e_w199773788-230_THA</t>
   </si>
   <si>
@@ -1129,19 +1174,25 @@
     <t>e_w259533943-500_THA,e_TH2-500_THA,e_TH1-500_THA</t>
   </si>
   <si>
-    <t>e_TH82-500_THA,e_w876135539-500_THA,e_TH81-230_THA</t>
-  </si>
-  <si>
-    <t>e_w334185872-230_THA,e_w262815047-230_THA,e_w254460966-230_THA,e_w631215304-230_THA,e_TH28-500_THA,e_w401936547-500_THA,e_w401936547-230_THA,e_w1192398379-230_THA,e_TH22-230_THA</t>
-  </si>
-  <si>
-    <t>e_w813762139-230_THA,e_w384684882-230_THA,e_w196803560-230_THA,e_TH16-230_THA,e_TH8-500_THA,e_TH7-500_THA,e_w551229222-230_THA,e_w259533943-500_THA,e_TH1-500_THA</t>
-  </si>
-  <si>
-    <t>e_w650122709-230_THA,e_TH71-500_THA,e_TH49-500_THA,e_TH74-230_THA,e_w404291513-230_THA,e_TH78-230_THA,e_w551510148-230_THA</t>
-  </si>
-  <si>
-    <t>e_w551510148-230_THA,e_TH44-230_THA,e_TH78-230_THA,e_w550657165-230_THA,e_w1387094571-230_THA</t>
+    <t>e_w573736537-230_THA,e_TH57-230_THA,e_w250742034-230_THA,e_w550825256-230_THA</t>
+  </si>
+  <si>
+    <t>e_w550224444-230_THA,e_TH13-500_THA,e_TH9-500_THA</t>
+  </si>
+  <si>
+    <t>e_w343034987-500_THA,e_w245311456-230_THA,e_w658003586-230_THA,e_w247878196-230_THA,e_w652927503-230_THA,e_w550709376-230_THA,e_w247704837-230_THA,e_w274497912-230_THA,e_TH15-230_THA</t>
+  </si>
+  <si>
+    <t>e_w404604266-230_THA,e_TH24-230_THA,e_TH23-230_THA,e_w550709376-230_THA,e_TH25-230_THA</t>
+  </si>
+  <si>
+    <t>e_w550665519-230_THA,e_w550709376-230_THA,e_w404604266-230_THA,e_w860769774-500_THA,e_w860769774-230_THA</t>
+  </si>
+  <si>
+    <t>e_w381850842-230_THA,e_TH84-500_THA,e_w381850832-230_THA,e_w381850842-500_THA,e_w239587274-230_THA,e_w550881475-230_THA,e_TH88-230_THA,e_TH83-500_THA,e_w1415498617-230_THA</t>
+  </si>
+  <si>
+    <t>e_w238578822-230_THA</t>
   </si>
   <si>
     <t>e_TH5-230_THA,e_TH17-230_THA,e_w1281883109-230_THA,e_w813762139-230_THA,e_TH6-230_THA</t>
@@ -1153,58 +1204,37 @@
     <t>e_w1357836334-230_THA,e_TH21-230_THA,e_TH19-230_THA,e_w254460966-230_THA,e_w401998847-230_THA,e_w550172093-230_THA,e_TH18-230_THA,e_TH14-500_THA,e_TH10-230_THA,e_w659646706-230_THA,e_w550224444-230_THA</t>
   </si>
   <si>
-    <t>e_w550665519-230_THA,e_w550709376-230_THA,e_w404604266-230_THA,e_w860769774-500_THA,e_w860769774-230_THA</t>
-  </si>
-  <si>
-    <t>e_TH31-230_THA,e_w1357836334-230_THA,e_w377077088-230_THA</t>
-  </si>
-  <si>
     <t>e_w550657165-230_THA,e_w550622477-230_THA,e_w550296523-230_THA,e_w1387094571-230_THA,e_w245311456-230_THA</t>
   </si>
   <si>
-    <t>e_TH17-230_THA,e_w1281883109-230_THA,e_TH31-230_THA,e_w377077088-230_THA</t>
-  </si>
-  <si>
-    <t>e_w343034987-500_THA,e_w245311456-230_THA,e_w658003586-230_THA,e_w247878196-230_THA,e_w652927503-230_THA,e_w550709376-230_THA,e_w247704837-230_THA,e_w274497912-230_THA,e_TH15-230_THA</t>
-  </si>
-  <si>
-    <t>e_w404604266-230_THA,e_TH24-230_THA,e_TH23-230_THA,e_w550709376-230_THA,e_TH25-230_THA</t>
-  </si>
-  <si>
-    <t>e_TH31-230_THA</t>
-  </si>
-  <si>
-    <t>e_w550152207-230_THA,e_w199773777-500_THA,e_w772281525-230_THA,e_TH75-230_THA,e_TH69-230_THA,e_w404006545-230_THA,e_w659641345-230_THA,e_w658704544-500_THA</t>
-  </si>
-  <si>
-    <t>e_w573736537-230_THA,e_TH57-230_THA,e_w250742034-230_THA,e_w550825256-230_THA</t>
-  </si>
-  <si>
-    <t>e_w550224444-230_THA,e_TH13-500_THA,e_TH9-500_THA</t>
-  </si>
-  <si>
-    <t>e_w550957004-230_THA,e_w1415498617-500_THA,e_TH86-230_THA,e_w550922890-230_THA,e_w244062167-230_THA,e_TH85-230_THA,e_w295988731-230_THA</t>
-  </si>
-  <si>
-    <t>e_TH47-230_THA,e_w404563246-230_THA,e_TH30-230_THA,e_w904473776-230_THA,e_w1364467990-230_THA,e_w550636268-230_THA,e_TH44-230_THA,e_w550657165-230_THA</t>
-  </si>
-  <si>
-    <t>e_w1281883109-230_THA</t>
-  </si>
-  <si>
-    <t>e_w324258748-230_THA,e_w238578822-230_THA,e_TH89-230_THA</t>
-  </si>
-  <si>
-    <t>e_TH22-230_THA,e_w659646706-230_THA,e_w550224444-230_THA,e_w550296523-230_THA,e_w659647773-230_THA,e_TH20-230_THA,e_w550257735-230_THA,e_TH13-500_THA,e_w382334126-230_THA,e_w343034987-500_THA,e_w382334127-230_THA,e_w247878196-230_THA,e_w245311456-230_THA</t>
-  </si>
-  <si>
-    <t>e_TH9-500_THA,e_w658429244-230_THA,e_w247704837-230_THA</t>
-  </si>
-  <si>
-    <t>e_w381850842-230_THA,e_TH84-500_THA,e_w381850832-230_THA,e_w381850842-500_THA,e_w239587274-230_THA,e_w550881475-230_THA,e_TH88-230_THA,e_TH83-500_THA,e_w1415498617-230_THA</t>
-  </si>
-  <si>
-    <t>e_w238578822-230_THA</t>
+    <t>distr_wonelc_won_THA_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_THA_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_THA_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_THA_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_THA_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
   </si>
   <si>
     <t>distr_wonelc_won_THA_013</t>
@@ -1213,28 +1243,10 @@
     <t>connecting wind onshore to buses in cluster 13</t>
   </si>
   <si>
-    <t>distr_wonelc_won_THA_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_THA_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_THA_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_THA_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
+    <t>distr_wonelc_won_THA_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
   </si>
   <si>
     <t>distr_wonelc_won_THA_005</t>
@@ -1255,46 +1267,64 @@
     <t>connecting wind onshore to buses in cluster 4</t>
   </si>
   <si>
+    <t>distr_wonelc_won_THA_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_THA_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_THA_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_THA_006</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 6</t>
   </si>
   <si>
-    <t>distr_wonelc_won_THA_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_THA_009</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 9</t>
   </si>
   <si>
-    <t>distr_wonelc_won_THA_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_THA_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_THA_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_THA_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
+    <t>elc_won_THA_015</t>
+  </si>
+  <si>
+    <t>e_TH80-230_THA,e_TH88-230_THA,e_w550862967-230_THA,e_TH79-230_THA,e_w876135539-500_THA,e_TH86-230_THA,e_TH81-230_THA</t>
+  </si>
+  <si>
+    <t>elc_won_THA_003</t>
+  </si>
+  <si>
+    <t>e_w550665519-230_THA,e_w247878196-230_THA,e_w245311456-230_THA,e_w550709376-230_THA,e_w652927503-230_THA,e_TH23-230_THA,e_TH25-230_THA</t>
+  </si>
+  <si>
+    <t>elc_won_THA_012</t>
+  </si>
+  <si>
+    <t>e_w650122709-230_THA,e_TH74-230_THA,e_TH78-230_THA</t>
+  </si>
+  <si>
+    <t>elc_won_THA_010</t>
+  </si>
+  <si>
+    <t>e_w573736537-230_THA</t>
+  </si>
+  <si>
+    <t>elc_won_THA_002</t>
+  </si>
+  <si>
+    <t>e_w652927503-230_THA,e_w274497912-230_THA</t>
   </si>
   <si>
     <t>elc_won_THA_013</t>
@@ -1303,28 +1333,10 @@
     <t>e_w234182441-230_THA,e_w388836605-500_THA,e_w250742034-230_THA,e_w550825256-230_THA</t>
   </si>
   <si>
-    <t>elc_won_THA_010</t>
-  </si>
-  <si>
-    <t>e_w573736537-230_THA</t>
-  </si>
-  <si>
-    <t>elc_won_THA_002</t>
-  </si>
-  <si>
-    <t>e_w652927503-230_THA,e_w274497912-230_THA</t>
-  </si>
-  <si>
-    <t>elc_won_THA_015</t>
-  </si>
-  <si>
-    <t>e_TH80-230_THA,e_TH88-230_THA,e_w550862967-230_THA,e_TH79-230_THA,e_w876135539-500_THA,e_TH86-230_THA,e_TH81-230_THA</t>
-  </si>
-  <si>
-    <t>elc_won_THA_003</t>
-  </si>
-  <si>
-    <t>e_w550665519-230_THA,e_w247878196-230_THA,e_w245311456-230_THA,e_w550709376-230_THA,e_w652927503-230_THA,e_TH23-230_THA,e_TH25-230_THA</t>
+    <t>elc_won_THA_011</t>
+  </si>
+  <si>
+    <t>e_w550152207-230_THA,e_TH75-230_THA,e_TH69-230_THA,e_w404006545-230_THA,e_TH71-500_THA,e_TH49-500_THA,e_w404291513-230_THA</t>
   </si>
   <si>
     <t>elc_won_THA_005</t>
@@ -1345,46 +1357,52 @@
     <t>e_w860769774-230_THA,e_w404604266-230_THA,e_TH24-230_THA,e_TH25-230_THA</t>
   </si>
   <si>
+    <t>elc_won_THA_014</t>
+  </si>
+  <si>
+    <t>e_w244062167-230_THA,e_TH89-230_THA,e_w238578822-230_THA</t>
+  </si>
+  <si>
+    <t>elc_won_THA_008</t>
+  </si>
+  <si>
+    <t>e_TH30-230_THA,e_w904473776-230_THA,e_w550636268-230_THA,e_w550296523-230_THA,e_w550657165-230_THA</t>
+  </si>
+  <si>
+    <t>elc_won_THA_007</t>
+  </si>
+  <si>
+    <t>e_w550622477-230_THA,e_w550296523-230_THA,e_w1387094571-230_THA,e_w382334126-230_THA,e_w245311456-230_THA</t>
+  </si>
+  <si>
     <t>elc_won_THA_006</t>
   </si>
   <si>
     <t>e_TH44-230_THA</t>
   </si>
   <si>
-    <t>elc_won_THA_014</t>
-  </si>
-  <si>
-    <t>e_w244062167-230_THA,e_TH89-230_THA,e_w238578822-230_THA</t>
-  </si>
-  <si>
     <t>elc_won_THA_009</t>
   </si>
   <si>
     <t>e_w631215304-230_THA,e_w772281525-230_THA,e_TH28-500_THA,e_w401936547-500_THA,e_w658704544-500_THA,e_w1192398379-230_THA</t>
   </si>
   <si>
-    <t>elc_won_THA_011</t>
-  </si>
-  <si>
-    <t>e_w550152207-230_THA,e_TH75-230_THA,e_TH69-230_THA,e_w404006545-230_THA,e_TH71-500_THA,e_TH49-500_THA,e_w404291513-230_THA</t>
-  </si>
-  <si>
-    <t>elc_won_THA_012</t>
-  </si>
-  <si>
-    <t>e_w650122709-230_THA,e_TH74-230_THA,e_TH78-230_THA</t>
-  </si>
-  <si>
-    <t>elc_won_THA_008</t>
-  </si>
-  <si>
-    <t>e_TH30-230_THA,e_w904473776-230_THA,e_w550636268-230_THA,e_w550296523-230_THA,e_w550657165-230_THA</t>
-  </si>
-  <si>
-    <t>elc_won_THA_007</t>
-  </si>
-  <si>
-    <t>e_w550622477-230_THA,e_w550296523-230_THA,e_w1387094571-230_THA,e_w382334126-230_THA,e_w245311456-230_THA</t>
+    <t>distr_wofelc_wof_THA_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_THA_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_THA_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
   </si>
   <si>
     <t>distr_wofelc_wof_THA_010</t>
@@ -1393,24 +1411,6 @@
     <t>connecting wind offshore to buses in cluster 10</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_THA_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_THA_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_THA_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_THA_008</t>
   </si>
   <si>
@@ -1423,6 +1423,18 @@
     <t>connecting wind offshore to buses in cluster 4</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_THA_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_THA_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_THA_009</t>
   </si>
   <si>
@@ -1435,16 +1447,19 @@
     <t>connecting wind offshore to buses in cluster 3</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_THA_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_THA_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
+    <t>elc_wof_THA_001</t>
+  </si>
+  <si>
+    <t>e_w234182441-230_THA,e_w388836605-500_THA</t>
+  </si>
+  <si>
+    <t>elc_wof_THA_006</t>
+  </si>
+  <si>
+    <t>e_w381850842-230_THA</t>
+  </si>
+  <si>
+    <t>elc_wof_THA_005</t>
   </si>
   <si>
     <t>elc_wof_THA_010</t>
@@ -1453,21 +1468,6 @@
     <t>e_w381850842-230_THA,e_TH84-500_THA</t>
   </si>
   <si>
-    <t>elc_wof_THA_006</t>
-  </si>
-  <si>
-    <t>e_w381850842-230_THA</t>
-  </si>
-  <si>
-    <t>elc_wof_THA_005</t>
-  </si>
-  <si>
-    <t>elc_wof_THA_001</t>
-  </si>
-  <si>
-    <t>e_w234182441-230_THA,e_w388836605-500_THA</t>
-  </si>
-  <si>
     <t>elc_wof_THA_008</t>
   </si>
   <si>
@@ -1480,22 +1480,22 @@
     <t>e_w550825256-230_THA,e_TH77-500_THA</t>
   </si>
   <si>
+    <t>elc_wof_THA_007</t>
+  </si>
+  <si>
+    <t>e_TH80-230_THA</t>
+  </si>
+  <si>
+    <t>elc_wof_THA_002</t>
+  </si>
+  <si>
+    <t>e_TH81-230_THA,e_w388836605-500_THA</t>
+  </si>
+  <si>
     <t>elc_wof_THA_009</t>
   </si>
   <si>
     <t>elc_wof_THA_003</t>
-  </si>
-  <si>
-    <t>elc_wof_THA_007</t>
-  </si>
-  <si>
-    <t>e_TH80-230_THA</t>
-  </si>
-  <si>
-    <t>elc_wof_THA_002</t>
-  </si>
-  <si>
-    <t>e_TH81-230_THA,e_w388836605-500_THA</t>
   </si>
   <si>
     <t>e_won_THA_001</t>
@@ -6851,7 +6851,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5B96904-DD39-4C02-B81E-C89BDCBFA47D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02CAB7C0-7291-4495-9474-DA9A70986E11}">
   <dimension ref="B9:BD39"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7089,16 +7089,16 @@
         <v>268</v>
       </c>
       <c r="Y11" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="Z11" t="s">
         <v>330</v>
       </c>
       <c r="AA11">
-        <v>0.99876738840114554</v>
+        <v>0.99839224467037746</v>
       </c>
       <c r="AB11">
-        <v>22.597879312332712</v>
+        <v>29.475514376412708</v>
       </c>
       <c r="AD11" t="s">
         <v>267</v>
@@ -7131,10 +7131,10 @@
         <v>390</v>
       </c>
       <c r="AO11">
-        <v>0.99735733005664406</v>
+        <v>0.99705002688642375</v>
       </c>
       <c r="AP11">
-        <v>48.448948961525012</v>
+        <v>54.082840415565052</v>
       </c>
       <c r="AR11" t="s">
         <v>267</v>
@@ -7167,10 +7167,10 @@
         <v>440</v>
       </c>
       <c r="BC11">
-        <v>0.98624454222014801</v>
+        <v>0.99460356115353721</v>
       </c>
       <c r="BD11">
-        <v>252.18339263061986</v>
+        <v>98.934712185150588</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -7235,16 +7235,16 @@
         <v>272</v>
       </c>
       <c r="Y12" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="Z12" t="s">
         <v>331</v>
       </c>
       <c r="AA12">
-        <v>0.99707652511683376</v>
+        <v>0.99781829751238382</v>
       </c>
       <c r="AB12">
-        <v>53.597039524713495</v>
+        <v>39.997878939629231</v>
       </c>
       <c r="AD12" t="s">
         <v>267</v>
@@ -7277,10 +7277,10 @@
         <v>392</v>
       </c>
       <c r="AO12">
-        <v>0.99928185462636432</v>
+        <v>0.99665101600741668</v>
       </c>
       <c r="AP12">
-        <v>13.165998516654131</v>
+        <v>61.398039864028398</v>
       </c>
       <c r="AR12" t="s">
         <v>267</v>
@@ -7381,16 +7381,16 @@
         <v>274</v>
       </c>
       <c r="Y13" t="s">
-        <v>239</v>
+        <v>255</v>
       </c>
       <c r="Z13" t="s">
         <v>332</v>
       </c>
       <c r="AA13">
-        <v>0.99670557242822921</v>
+        <v>0.997211573749749</v>
       </c>
       <c r="AB13">
-        <v>60.397838815796817</v>
+        <v>51.121147921268253</v>
       </c>
       <c r="AD13" t="s">
         <v>267</v>
@@ -7423,10 +7423,10 @@
         <v>394</v>
       </c>
       <c r="AO13">
-        <v>0.99604093556323714</v>
+        <v>0.99902641097279166</v>
       </c>
       <c r="AP13">
-        <v>72.582848007318702</v>
+        <v>17.849132165486964</v>
       </c>
       <c r="AR13" t="s">
         <v>267</v>
@@ -7527,16 +7527,16 @@
         <v>276</v>
       </c>
       <c r="Y14" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="Z14" t="s">
         <v>333</v>
       </c>
       <c r="AA14">
-        <v>0.99839224467037746</v>
+        <v>0.9967456350142726</v>
       </c>
       <c r="AB14">
-        <v>29.475514376412708</v>
+        <v>59.66335807166805</v>
       </c>
       <c r="AD14" t="s">
         <v>267</v>
@@ -7569,10 +7569,10 @@
         <v>396</v>
       </c>
       <c r="AO14">
-        <v>0.99705002688642375</v>
+        <v>0.99928185462636432</v>
       </c>
       <c r="AP14">
-        <v>54.082840415565052</v>
+        <v>13.165998516654131</v>
       </c>
       <c r="AR14" t="s">
         <v>267</v>
@@ -7605,10 +7605,10 @@
         <v>445</v>
       </c>
       <c r="BC14">
-        <v>0.99460356115353721</v>
+        <v>0.98624454222014801</v>
       </c>
       <c r="BD14">
-        <v>98.934712185150588</v>
+        <v>252.18339263061986</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -7673,16 +7673,16 @@
         <v>278</v>
       </c>
       <c r="Y15" t="s">
-        <v>265</v>
+        <v>252</v>
       </c>
       <c r="Z15" t="s">
         <v>334</v>
       </c>
       <c r="AA15">
-        <v>0.99781829751238382</v>
+        <v>0.99778853646104326</v>
       </c>
       <c r="AB15">
-        <v>39.997878939629231</v>
+        <v>40.543498214206487</v>
       </c>
       <c r="AD15" t="s">
         <v>267</v>
@@ -7715,10 +7715,10 @@
         <v>398</v>
       </c>
       <c r="AO15">
-        <v>0.99665101600741668</v>
+        <v>0.99604093556323714</v>
       </c>
       <c r="AP15">
-        <v>61.398039864028398</v>
+        <v>72.582848007318702</v>
       </c>
       <c r="AR15" t="s">
         <v>267</v>
@@ -7819,16 +7819,16 @@
         <v>280</v>
       </c>
       <c r="Y16" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="Z16" t="s">
         <v>335</v>
       </c>
       <c r="AA16">
-        <v>0.997211573749749</v>
+        <v>0.99847319647949806</v>
       </c>
       <c r="AB16">
-        <v>51.121147921268253</v>
+        <v>27.991397875867904</v>
       </c>
       <c r="AD16" t="s">
         <v>267</v>
@@ -7861,10 +7861,10 @@
         <v>400</v>
       </c>
       <c r="AO16">
-        <v>0.9970275833202018</v>
+        <v>0.99735733005664406</v>
       </c>
       <c r="AP16">
-        <v>54.494305796301134</v>
+        <v>48.448948961525012</v>
       </c>
       <c r="AR16" t="s">
         <v>267</v>
@@ -8007,10 +8007,10 @@
         <v>402</v>
       </c>
       <c r="AO17">
-        <v>0.99746219813692838</v>
+        <v>0.99840747784060091</v>
       </c>
       <c r="AP17">
-        <v>46.52636748964737</v>
+        <v>29.196239588983293</v>
       </c>
       <c r="AR17" t="s">
         <v>267</v>
@@ -8040,13 +8040,13 @@
         <v>450</v>
       </c>
       <c r="BB17" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="BC17">
-        <v>0.98437449440056546</v>
+        <v>0.98922420864143334</v>
       </c>
       <c r="BD17">
-        <v>286.46760265629888</v>
+        <v>197.55617490705433</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -8153,10 +8153,10 @@
         <v>404</v>
       </c>
       <c r="AO18">
-        <v>0.99877344283335923</v>
+        <v>0.9970275833202018</v>
       </c>
       <c r="AP18">
-        <v>22.486881388413671</v>
+        <v>54.494305796301134</v>
       </c>
       <c r="AR18" t="s">
         <v>267</v>
@@ -8183,16 +8183,16 @@
         <v>433</v>
       </c>
       <c r="BA18" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="BB18" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="BC18">
-        <v>0.992822597057193</v>
+        <v>0.9914493471334701</v>
       </c>
       <c r="BD18">
-        <v>131.5857206181276</v>
+        <v>156.76196921971376</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -8257,16 +8257,16 @@
         <v>286</v>
       </c>
       <c r="Y19" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="Z19" t="s">
         <v>338</v>
       </c>
       <c r="AA19">
-        <v>0.99792124920113712</v>
+        <v>0.99351066429364954</v>
       </c>
       <c r="AB19">
-        <v>38.110431312485566</v>
+        <v>118.9711546164249</v>
       </c>
       <c r="AD19" t="s">
         <v>267</v>
@@ -8299,10 +8299,10 @@
         <v>406</v>
       </c>
       <c r="AO19">
-        <v>0.99639700456189362</v>
+        <v>0.99746219813692838</v>
       </c>
       <c r="AP19">
-        <v>66.054916365283376</v>
+        <v>46.52636748964737</v>
       </c>
       <c r="AR19" t="s">
         <v>267</v>
@@ -8329,16 +8329,16 @@
         <v>435</v>
       </c>
       <c r="BA19" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="BB19" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="BC19">
-        <v>0.98922420864143334</v>
+        <v>0.98437449440056546</v>
       </c>
       <c r="BD19">
-        <v>197.55617490705433</v>
+        <v>286.46760265629888</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -8403,16 +8403,16 @@
         <v>288</v>
       </c>
       <c r="Y20" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="Z20" t="s">
         <v>339</v>
       </c>
       <c r="AA20">
-        <v>0.99717520082312683</v>
+        <v>0.99671686091376932</v>
       </c>
       <c r="AB20">
-        <v>51.787984909341745</v>
+        <v>60.190883247563136</v>
       </c>
       <c r="AD20" t="s">
         <v>267</v>
@@ -8445,10 +8445,10 @@
         <v>408</v>
       </c>
       <c r="AO20">
-        <v>0.99840641024894017</v>
+        <v>0.99877344283335923</v>
       </c>
       <c r="AP20">
-        <v>29.215812102764456</v>
+        <v>22.486881388413671</v>
       </c>
       <c r="AR20" t="s">
         <v>267</v>
@@ -8475,16 +8475,16 @@
         <v>437</v>
       </c>
       <c r="BA20" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="BB20" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="BC20">
-        <v>0.9914493471334701</v>
+        <v>0.992822597057193</v>
       </c>
       <c r="BD20">
-        <v>156.76196921971376</v>
+        <v>131.5857206181276</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -8549,16 +8549,16 @@
         <v>290</v>
       </c>
       <c r="Y21" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Z21" t="s">
         <v>340</v>
       </c>
       <c r="AA21">
-        <v>0.99793970259117548</v>
+        <v>0.99926998166189085</v>
       </c>
       <c r="AB21">
-        <v>37.772119161782747</v>
+        <v>13.383669532000935</v>
       </c>
       <c r="AD21" t="s">
         <v>267</v>
@@ -8591,10 +8591,10 @@
         <v>410</v>
       </c>
       <c r="AO21">
-        <v>0.99831121883390661</v>
+        <v>0.99840641024894017</v>
       </c>
       <c r="AP21">
-        <v>30.960988045045038</v>
+        <v>29.215812102764456</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -8659,16 +8659,16 @@
         <v>292</v>
       </c>
       <c r="Y22" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="Z22" t="s">
         <v>341</v>
       </c>
       <c r="AA22">
-        <v>0.99709397299495006</v>
+        <v>0.99341953531771376</v>
       </c>
       <c r="AB22">
-        <v>53.277161759249672</v>
+        <v>120.64185250858044</v>
       </c>
       <c r="AD22" t="s">
         <v>267</v>
@@ -8701,10 +8701,10 @@
         <v>412</v>
       </c>
       <c r="AO22">
-        <v>0.99840747784060091</v>
+        <v>0.99768002559775337</v>
       </c>
       <c r="AP22">
-        <v>29.196239588983293</v>
+        <v>42.532864041187544</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -8769,16 +8769,16 @@
         <v>294</v>
       </c>
       <c r="Y23" t="s">
-        <v>261</v>
+        <v>250</v>
       </c>
       <c r="Z23" t="s">
         <v>342</v>
       </c>
       <c r="AA23">
-        <v>0.9967456350142726</v>
+        <v>0.99741947421254784</v>
       </c>
       <c r="AB23">
-        <v>59.66335807166805</v>
+        <v>47.309639436623094</v>
       </c>
       <c r="AD23" t="s">
         <v>267</v>
@@ -8811,10 +8811,10 @@
         <v>414</v>
       </c>
       <c r="AO23">
-        <v>0.99902641097279166</v>
+        <v>0.9974605247986873</v>
       </c>
       <c r="AP23">
-        <v>17.849132165486964</v>
+        <v>46.55704535739882</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -8879,16 +8879,16 @@
         <v>296</v>
       </c>
       <c r="Y24" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Z24" t="s">
         <v>343</v>
       </c>
       <c r="AA24">
-        <v>0.99760835216442434</v>
+        <v>0.99740306455094896</v>
       </c>
       <c r="AB24">
-        <v>43.846876985553521</v>
+        <v>47.610483232603059</v>
       </c>
       <c r="AD24" t="s">
         <v>267</v>
@@ -8921,10 +8921,10 @@
         <v>416</v>
       </c>
       <c r="AO24">
-        <v>0.99768002559775337</v>
+        <v>0.99639700456189362</v>
       </c>
       <c r="AP24">
-        <v>42.532864041187544</v>
+        <v>66.054916365283376</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -8989,16 +8989,16 @@
         <v>298</v>
       </c>
       <c r="Y25" t="s">
-        <v>259</v>
+        <v>237</v>
       </c>
       <c r="Z25" t="s">
         <v>344</v>
       </c>
       <c r="AA25">
-        <v>0.99351066429364954</v>
+        <v>0.99768939826239855</v>
       </c>
       <c r="AB25">
-        <v>118.9711546164249</v>
+        <v>42.361031856025839</v>
       </c>
       <c r="AD25" t="s">
         <v>267</v>
@@ -9031,10 +9031,10 @@
         <v>418</v>
       </c>
       <c r="AO25">
-        <v>0.9974605247986873</v>
+        <v>0.99831121883390661</v>
       </c>
       <c r="AP25">
-        <v>46.55704535739882</v>
+        <v>30.960988045045038</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -9099,16 +9099,16 @@
         <v>300</v>
       </c>
       <c r="Y26" t="s">
-        <v>238</v>
+        <v>263</v>
       </c>
       <c r="Z26" t="s">
         <v>345</v>
       </c>
       <c r="AA26">
-        <v>0.9975577095120135</v>
+        <v>0.99876738840114554</v>
       </c>
       <c r="AB26">
-        <v>44.775325613085109</v>
+        <v>22.597879312332712</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -9173,16 +9173,16 @@
         <v>302</v>
       </c>
       <c r="Y27" t="s">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="Z27" t="s">
         <v>346</v>
       </c>
       <c r="AA27">
-        <v>0.99681299742416585</v>
+        <v>0.99707652511683376</v>
       </c>
       <c r="AB27">
-        <v>58.428380556958672</v>
+        <v>53.597039524713495</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -9247,16 +9247,16 @@
         <v>304</v>
       </c>
       <c r="Y28" t="s">
-        <v>260</v>
+        <v>239</v>
       </c>
       <c r="Z28" t="s">
         <v>347</v>
       </c>
       <c r="AA28">
-        <v>0.99671686091376932</v>
+        <v>0.99670557242822921</v>
       </c>
       <c r="AB28">
-        <v>60.190883247563136</v>
+        <v>60.397838815796817</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -9321,16 +9321,16 @@
         <v>306</v>
       </c>
       <c r="Y29" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="Z29" t="s">
         <v>348</v>
       </c>
       <c r="AA29">
-        <v>0.99926998166189085</v>
+        <v>0.99768298013990064</v>
       </c>
       <c r="AB29">
-        <v>13.383669532000935</v>
+        <v>42.478697435155169</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -9395,16 +9395,16 @@
         <v>308</v>
       </c>
       <c r="Y30" t="s">
-        <v>258</v>
+        <v>240</v>
       </c>
       <c r="Z30" t="s">
         <v>349</v>
       </c>
       <c r="AA30">
-        <v>0.99768298013990064</v>
+        <v>0.9968514169155549</v>
       </c>
       <c r="AB30">
-        <v>42.478697435155169</v>
+        <v>57.72402321482614</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -9469,16 +9469,16 @@
         <v>310</v>
       </c>
       <c r="Y31" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="Z31" t="s">
         <v>350</v>
       </c>
       <c r="AA31">
-        <v>0.9968514169155549</v>
+        <v>0.9975577095120135</v>
       </c>
       <c r="AB31">
-        <v>57.72402321482614</v>
+        <v>44.775325613085109</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -9543,16 +9543,16 @@
         <v>312</v>
       </c>
       <c r="Y32" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="Z32" t="s">
         <v>351</v>
       </c>
       <c r="AA32">
-        <v>0.99778853646104326</v>
+        <v>0.99681299742416585</v>
       </c>
       <c r="AB32">
-        <v>40.543498214206487</v>
+        <v>58.428380556958672</v>
       </c>
     </row>
     <row r="33" spans="2:28">
@@ -9617,16 +9617,16 @@
         <v>314</v>
       </c>
       <c r="Y33" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="Z33" t="s">
         <v>352</v>
       </c>
       <c r="AA33">
-        <v>0.99847319647949806</v>
+        <v>0.99709397299495006</v>
       </c>
       <c r="AB33">
-        <v>27.991397875867904</v>
+        <v>53.277161759249672</v>
       </c>
     </row>
     <row r="34" spans="2:28">
@@ -9691,16 +9691,16 @@
         <v>316</v>
       </c>
       <c r="Y34" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="Z34" t="s">
         <v>353</v>
       </c>
       <c r="AA34">
-        <v>0.99341953531771376</v>
+        <v>0.99872479363303079</v>
       </c>
       <c r="AB34">
-        <v>120.64185250858044</v>
+        <v>23.378783394434638</v>
       </c>
     </row>
     <row r="35" spans="2:28">
@@ -9765,16 +9765,16 @@
         <v>318</v>
       </c>
       <c r="Y35" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="Z35" t="s">
         <v>354</v>
       </c>
       <c r="AA35">
-        <v>0.99741947421254784</v>
+        <v>0.99576861575556042</v>
       </c>
       <c r="AB35">
-        <v>47.309639436623094</v>
+        <v>77.575377814725385</v>
       </c>
     </row>
     <row r="36" spans="2:28">
@@ -9839,16 +9839,16 @@
         <v>320</v>
       </c>
       <c r="Y36" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="Z36" t="s">
         <v>355</v>
       </c>
       <c r="AA36">
-        <v>0.99740306455094896</v>
+        <v>0.99792124920113712</v>
       </c>
       <c r="AB36">
-        <v>47.610483232603059</v>
+        <v>38.110431312485566</v>
       </c>
     </row>
     <row r="37" spans="2:28">
@@ -9913,16 +9913,16 @@
         <v>322</v>
       </c>
       <c r="Y37" t="s">
-        <v>237</v>
+        <v>257</v>
       </c>
       <c r="Z37" t="s">
         <v>356</v>
       </c>
       <c r="AA37">
-        <v>0.99768939826239855</v>
+        <v>0.99717520082312683</v>
       </c>
       <c r="AB37">
-        <v>42.361031856025839</v>
+        <v>51.787984909341745</v>
       </c>
     </row>
     <row r="38" spans="2:28">
@@ -9987,16 +9987,16 @@
         <v>324</v>
       </c>
       <c r="Y38" t="s">
-        <v>249</v>
+        <v>262</v>
       </c>
       <c r="Z38" t="s">
         <v>357</v>
       </c>
       <c r="AA38">
-        <v>0.99872479363303079</v>
+        <v>0.99793970259117548</v>
       </c>
       <c r="AB38">
-        <v>23.378783394434638</v>
+        <v>37.772119161782747</v>
       </c>
     </row>
     <row r="39" spans="2:28">
@@ -10061,16 +10061,16 @@
         <v>326</v>
       </c>
       <c r="Y39" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="Z39" t="s">
         <v>358</v>
       </c>
       <c r="AA39">
-        <v>0.99576861575556042</v>
+        <v>0.99760835216442434</v>
       </c>
       <c r="AB39">
-        <v>77.575377814725385</v>
+        <v>43.846876985553521</v>
       </c>
     </row>
   </sheetData>
@@ -10079,7 +10079,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{901E437D-0676-4E14-8201-502E231C5470}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57681D67-F929-4BA3-BA4C-EAB60B402560}">
   <dimension ref="B9:Z25"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -10191,7 +10191,7 @@
         <v>456</v>
       </c>
       <c r="K11" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="L11">
         <v>1.4377041993130946</v>
@@ -10224,7 +10224,7 @@
         <v>486</v>
       </c>
       <c r="X11" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="Y11">
         <v>7.3125</v>
@@ -10259,7 +10259,7 @@
         <v>458</v>
       </c>
       <c r="K12" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="L12">
         <v>3.0693757199731246</v>
@@ -10292,7 +10292,7 @@
         <v>488</v>
       </c>
       <c r="X12" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="Y12">
         <v>20.721</v>
@@ -10327,7 +10327,7 @@
         <v>460</v>
       </c>
       <c r="K13" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="L13">
         <v>12.127188821973427</v>
@@ -10360,7 +10360,7 @@
         <v>490</v>
       </c>
       <c r="X13" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="Y13">
         <v>8.1989999999999998</v>
@@ -10395,7 +10395,7 @@
         <v>462</v>
       </c>
       <c r="K14" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="L14">
         <v>3.9669096575423799</v>
@@ -10463,7 +10463,7 @@
         <v>464</v>
       </c>
       <c r="K15" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="L15">
         <v>5.772579134171945</v>
@@ -10531,7 +10531,7 @@
         <v>466</v>
       </c>
       <c r="K16" t="s">
-        <v>405</v>
+        <v>415</v>
       </c>
       <c r="L16">
         <v>3.888439349126517</v>
@@ -10599,7 +10599,7 @@
         <v>468</v>
       </c>
       <c r="K17" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="L17">
         <v>6.7771312454737487</v>
@@ -10632,7 +10632,7 @@
         <v>498</v>
       </c>
       <c r="X17" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="Y17">
         <v>11.226749999999999</v>
@@ -10667,7 +10667,7 @@
         <v>470</v>
       </c>
       <c r="K18" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="L18">
         <v>2.8025446752858327</v>
@@ -10735,7 +10735,7 @@
         <v>472</v>
       </c>
       <c r="K19" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="L19">
         <v>3.9761038964540143</v>
@@ -10768,7 +10768,7 @@
         <v>502</v>
       </c>
       <c r="X19" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="Y19">
         <v>10.906499999999999</v>
@@ -10803,7 +10803,7 @@
         <v>474</v>
       </c>
       <c r="K20" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="L20">
         <v>0.15760337762888244</v>
@@ -10836,7 +10836,7 @@
         <v>504</v>
       </c>
       <c r="X20" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="Y20">
         <v>14.325749999999999</v>
@@ -10871,7 +10871,7 @@
         <v>476</v>
       </c>
       <c r="K21" t="s">
-        <v>411</v>
+        <v>401</v>
       </c>
       <c r="L21">
         <v>0.72151273501932833</v>
@@ -10906,7 +10906,7 @@
         <v>478</v>
       </c>
       <c r="K22" t="s">
-        <v>413</v>
+        <v>393</v>
       </c>
       <c r="L22">
         <v>3.528030723227827E-2</v>
@@ -10941,7 +10941,7 @@
         <v>480</v>
       </c>
       <c r="K23" t="s">
-        <v>389</v>
+        <v>399</v>
       </c>
       <c r="L23">
         <v>0.60991119750629252</v>
@@ -10976,7 +10976,7 @@
         <v>482</v>
       </c>
       <c r="K24" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="L24">
         <v>2.4362222513874092E-2</v>
@@ -11011,7 +11011,7 @@
         <v>484</v>
       </c>
       <c r="K25" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="L25">
         <v>0.37595534787165791</v>
@@ -11026,7 +11026,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8CAE705-FA39-4446-B139-4A68B48CC392}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54C76F67-9B97-47C7-969B-B2433229B20F}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -12843,7 +12843,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46BF39B8-0E58-4E19-AC72-183E9AAF6885}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F929D82-899F-4E29-B3AE-3C7AD29292FD}">
   <dimension ref="B2:M47"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
